--- a/SGC-CKN/Excel/ad142dc4-a3f3-4ed0-8b4d-5a5e37aecf89_Lô_CT-02_P7-114_D800_09-04-2026.xlsx
+++ b/SGC-CKN/Excel/ad142dc4-a3f3-4ed0-8b4d-5a5e37aecf89_Lô_CT-02_P7-114_D800_09-04-2026.xlsx
@@ -115,7 +115,7 @@
     <t>Cát pha xám ghi, xám nâu TT dẻo</t>
   </si>
   <si>
-    <t xml:space="preserve">22:40
+    <t xml:space="preserve">22:30
 08/04/2026</t>
   </si>
   <si>
@@ -1209,7 +1209,7 @@
         <v>29</v>
       </c>
       <c r="F11" s="5">
-        <v>-0.7</v>
+        <v>0</v>
       </c>
       <c r="G11" s="5">
         <v>-7.2</v>
@@ -1218,10 +1218,10 @@
         <v>1</v>
       </c>
       <c r="I11" s="5">
-        <v>6.5</v>
+        <v>7.2</v>
       </c>
       <c r="J11" s="8">
-        <v>6.5</v>
+        <v>7.2</v>
       </c>
       <c r="K11" s="6" t="s">
         <v>30</v>
@@ -1250,13 +1250,13 @@
         <v>-9.65</v>
       </c>
       <c r="H12" s="9">
-        <v>1.17</v>
+        <v>1</v>
       </c>
       <c r="I12" s="9">
         <v>2.45</v>
       </c>
       <c r="J12" s="12">
-        <v>2.1</v>
+        <v>2.45</v>
       </c>
       <c r="K12" s="10" t="s">
         <v>34</v>
@@ -1282,16 +1282,16 @@
         <v>-9.65</v>
       </c>
       <c r="G13" s="13">
-        <v>-18.26</v>
+        <v>-17.26</v>
       </c>
       <c r="H13" s="13">
-        <v>2.67</v>
+        <v>2.83</v>
       </c>
       <c r="I13" s="13">
-        <v>8.61</v>
+        <v>7.61</v>
       </c>
       <c r="J13" s="12">
-        <v>3.23</v>
+        <v>2.69</v>
       </c>
       <c r="K13" s="14" t="s">
         <v>34</v>
@@ -1314,7 +1314,7 @@
         <v>40</v>
       </c>
       <c r="F14" s="16">
-        <v>-18.26</v>
+        <v>-17.26</v>
       </c>
       <c r="G14" s="16">
         <v>-21.5</v>
@@ -1323,10 +1323,10 @@
         <v>0.67</v>
       </c>
       <c r="I14" s="16">
-        <v>3.24</v>
-      </c>
-      <c r="J14" s="12">
-        <v>4.86</v>
+        <v>4.24</v>
+      </c>
+      <c r="J14" s="8">
+        <v>6.36</v>
       </c>
       <c r="K14" s="17" t="s">
         <v>34</v>
@@ -1691,7 +1691,7 @@
         <v>1</v>
       </c>
       <c r="E2" s="5">
-        <v>-0.7</v>
+        <v>0</v>
       </c>
       <c r="F2" s="5">
         <v>-7.2</v>
@@ -1700,10 +1700,10 @@
         <v>1</v>
       </c>
       <c r="H2" s="5">
-        <v>6.5</v>
+        <v>7.2</v>
       </c>
       <c r="I2" s="8">
-        <v>6.5</v>
+        <v>7.2</v>
       </c>
     </row>
     <row r="3" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -1726,13 +1726,13 @@
         <v>-9.65</v>
       </c>
       <c r="G3" s="9">
-        <v>1.17</v>
+        <v>1</v>
       </c>
       <c r="H3" s="9">
         <v>2.45</v>
       </c>
       <c r="I3" s="12">
-        <v>2.1</v>
+        <v>2.45</v>
       </c>
     </row>
     <row r="4" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -1752,16 +1752,16 @@
         <v>-9.65</v>
       </c>
       <c r="F4" s="13">
-        <v>-18.26</v>
+        <v>-17.26</v>
       </c>
       <c r="G4" s="13">
-        <v>2.67</v>
+        <v>2.83</v>
       </c>
       <c r="H4" s="13">
-        <v>8.61</v>
+        <v>7.61</v>
       </c>
       <c r="I4" s="12">
-        <v>3.23</v>
+        <v>2.69</v>
       </c>
     </row>
     <row r="5" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -1778,7 +1778,7 @@
         <v>1</v>
       </c>
       <c r="E5" s="16">
-        <v>-18.26</v>
+        <v>-17.26</v>
       </c>
       <c r="F5" s="16">
         <v>-21.5</v>
@@ -1787,10 +1787,10 @@
         <v>0.67</v>
       </c>
       <c r="H5" s="16">
-        <v>3.24</v>
-      </c>
-      <c r="I5" s="12">
-        <v>4.86</v>
+        <v>4.24</v>
+      </c>
+      <c r="I5" s="8">
+        <v>6.36</v>
       </c>
     </row>
     <row r="6" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -1981,7 +1981,7 @@
         <v>10</v>
       </c>
       <c r="E12" s="39">
-        <v>-0.7</v>
+        <v>0</v>
       </c>
       <c r="F12" s="39">
         <v>-44.78</v>
@@ -1990,10 +1990,10 @@
         <v>9.17</v>
       </c>
       <c r="H12" s="39">
-        <v>44.08</v>
+        <v>44.78</v>
       </c>
       <c r="I12" s="39">
-        <v>4.81</v>
+        <v>4.89</v>
       </c>
     </row>
   </sheetData>
